--- a/dados/enviadas/Rodobens.xlsx
+++ b/dados/enviadas/Rodobens.xlsx
@@ -1,53 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tec01\Desktop\pasta_de_trabalho\auto_painel\dados\enviadas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3781D3AB-2F88-4912-8142-DFE609C573C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$7</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+  <si>
+    <t>CLIENTE</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>MODALIDADE</t>
+  </si>
+  <si>
+    <t>VALOR_ESTIMADO</t>
+  </si>
+  <si>
+    <t>ORGAO</t>
+  </si>
+  <si>
+    <t>DATA_DISPUTA</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>LINK_PORTAL</t>
+  </si>
+  <si>
+    <t>LINK_PNCP</t>
+  </si>
+  <si>
+    <t>Rodobens</t>
+  </si>
+  <si>
+    <t>27/2026</t>
+  </si>
+  <si>
+    <t>Vans</t>
+  </si>
+  <si>
+    <t>Pregão - Eletrônico</t>
+  </si>
+  <si>
+    <t>MUNICIPIO DE BURITIS</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>AMM Licita</t>
+  </si>
+  <si>
+    <t>https://app2.ammlicita.org.br/pesquisa/113754</t>
+  </si>
+  <si>
+    <t>https://pncp.gov.br/app/editais/18125146000129/2026/75</t>
+  </si>
+  <si>
+    <t>068/2026</t>
+  </si>
+  <si>
+    <t>Veículos diversos</t>
+  </si>
+  <si>
+    <t>MUNICIPIO DE ITURAMA</t>
+  </si>
+  <si>
+    <t>Licitanet</t>
+  </si>
+  <si>
+    <t>https://licitanet.com.br/sessao/197624</t>
+  </si>
+  <si>
+    <t>https://pncp.gov.br/app/editais/18457242000174/2026/50</t>
+  </si>
+  <si>
+    <t>121566/2026</t>
+  </si>
+  <si>
+    <t>ESTADO DE GOIAS</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>https://pncp.gov.br/app/editais/01409580000138/2026/1504</t>
+  </si>
+  <si>
+    <t>007/2026</t>
+  </si>
+  <si>
+    <t>FUNDO MUNICIPAL DE SAUDE - FMS</t>
+  </si>
+  <si>
+    <t>BNC Compras</t>
+  </si>
+  <si>
+    <t>https://bnccompras.com/Process/ProcessView?param1=[gkz]t2u5cIzj/xhS1SrMk0GEHPEPQM5Trgtqzylqde8yoEApMz7710r9o0MDC6SFyUfoDuky8U36oGK_epjkUF4FfxLd_mvEit3UdNS2/c1MXuA=</t>
+  </si>
+  <si>
+    <t>https://pncp.gov.br/app/editais/69902112000134/2026/15</t>
+  </si>
+  <si>
+    <t>PE 40/2026</t>
+  </si>
+  <si>
+    <t>MUNICIPIO DE VILA RICA</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>https://pncp.gov.br/app/editais/03238862000145/2026/84</t>
+  </si>
+  <si>
+    <t>90/2026</t>
+  </si>
+  <si>
+    <t>SUP. EST. DE LICITACAO</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>ComprasGov</t>
+  </si>
+  <si>
+    <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=92537305000902026</t>
+  </si>
+  <si>
+    <t>https://pncp.gov.br/app/editais/04696490000163/2026/132</t>
+  </si>
+  <si>
+    <t>https://sislog.go.gov.br/</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$R$-416] #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$R$-416]\ #,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,105 +207,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -446,166 +540,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="53" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="59" customWidth="1" min="9" max="9"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="10" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>CLIENTE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>MODALIDADE</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>VALOR_ESTIMADO</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>ORGAO</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>DATA_DISPUTA</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>LINK_PORTAL</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>LINK_PNCP</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Rodobens</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>018/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2586288</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ENGENHEIRO CALDAS</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>BLL Compras</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>https://bllcompras.com/Process/ProcessView?param1=[gkz]wpX4yaHNo96WJP7RvIhSXuxUSANlBbWrwza/S9PG1WBMIS0PRSbKKf6HGAWYWMK1aMrfcT_F6vwHMcdtOH2aKOsearLctBrUsj6A5iySk_E=</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18080655000182/2026/71</t>
-        </is>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2162000</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Rodobens</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>SP114/2026/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Sigiloso</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>EMPRESA BAIANA DE AGUAS E SANEAMENTO S/A - EMBASA</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Novo Banco do Brasil</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>https://licitacoes-e2.bb.com.br/aop-inter-estatico/visualizar-processo-publico/1097583</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/13504675000110/2026/212</t>
-        </is>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1657629.5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46293</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4861883.0999999996</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46309</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3">
+        <v>154900</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46309</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3">
+        <v>418740.97</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3">
+        <v>960000</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:J7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>